--- a/apps/web/public/importmallar/importmall-leverantorer.xlsx
+++ b/apps/web/public/importmallar/importmall-leverantorer.xlsx
@@ -82,7 +82,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Leverantörens e-postadress (dit förfrågningar och inköpsorder skickas), max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Leverantörens e-postadress (dit förfrågningar och inköpsorder skickas), max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </r>
       </text>
     </comment>
@@ -166,7 +166,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Leverantörens katalogpriser och inköpsorder anges i valutan. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
+          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya inköpsorder och nya katalograder (även de som Inköpspriser-importen skapar) får leverantörens valuta; befintliga behåller sin. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
         </r>
       </text>
     </comment>
@@ -269,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -278,6 +278,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -289,24 +290,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1" style="4"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="3" max="3" width="23" customWidth="1" style="4"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1" style="4"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1" style="4"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="21" customWidth="1"/>
-    <col min="16" max="16" width="19" customWidth="1"/>
-    <col min="17" max="17" width="25" customWidth="1"/>
-    <col min="18" max="18" width="27" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1" style="4"/>
+    <col min="14" max="14" width="19" customWidth="1" style="4"/>
+    <col min="15" max="15" width="21" customWidth="1" style="4"/>
+    <col min="16" max="16" width="19" customWidth="1" style="4"/>
+    <col min="17" max="17" width="25" customWidth="1" style="4"/>
+    <col min="18" max="18" width="27" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -434,88 +435,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leverantörsnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Leverantörens unika nummer, max 50 tecken. Finns numret redan uppdateras leverantören, annars skapas en ny. Nummerserien för leverantörer flyttas fram förbi filens högsta rent numeriska nummer.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2001</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Namn</t>
+          <t xml:space="preserve">Leverantörsnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörens namn, max 255 tecken. Krävs för nya leverantörer. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Leverantörens unika nummer, max 50 tecken. Finns numret redan uppdateras leverantören, annars skapas en ny. Nummerserien för leverantörer flyttas fram förbi filens högsta rent numeriska nummer.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempel Stålhandel AB</t>
+          <t xml:space="preserve">2001</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organisationsnummer</t>
+          <t xml:space="preserve">Namn</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -525,19 +511,19 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Leverantörens namn, max 255 tecken. Krävs för nya leverantörer. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">556987-6543</t>
+          <t xml:space="preserve">Exempel Stålhandel AB</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAT-nummer</t>
+          <t xml:space="preserve">Organisationsnummer</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -547,19 +533,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Momsregistreringsnummer, max 30 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE556987654301</t>
+          <t xml:space="preserve">556987-6543</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktperson</t>
+          <t xml:space="preserve">VAT-nummer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -569,19 +555,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kontaktpersonens namn på leverantörskortets Allmänt-flik, max 255 tecken — kontaktregistret importeras separat som leverantörskontakter.</t>
+          <t xml:space="preserve">Momsregistreringsnummer, max 30 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bo Bengtsson</t>
+          <t xml:space="preserve">SE556987654301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">E-post</t>
+          <t xml:space="preserve">Kontaktperson</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -591,19 +577,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leverantörens e-postadress (dit förfrågningar och inköpsorder skickas), max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt med en varning.</t>
+          <t xml:space="preserve">Kontaktpersonens namn på leverantörskortets Allmänt-flik, max 255 tecken — kontaktregistret importeras separat som leverantörskontakter.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">order@example.com</t>
+          <t xml:space="preserve">Bo Bengtsson</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telefon</t>
+          <t xml:space="preserve">E-post</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -613,19 +599,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Leverantörens e-postadress (dit förfrågningar och inköpsorder skickas), max 255 tecken. En ogiltig adress stoppar inte raden — fältet lämnas tomt på en ny post och orört på en befintlig, med en varning.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010-100 10 10</t>
+          <t xml:space="preserve">order@example.com</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adress</t>
+          <t xml:space="preserve">Telefon</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -635,19 +621,19 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postadressens första rad. Adress, Adressrad 2 och Adressrad 3 slås ihop till en adress med radbrytningar; är alla tre tomma lämnas adressen orörd.</t>
+          <t xml:space="preserve">Max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valsverksgatan 4</t>
+          <t xml:space="preserve">010-100 10 10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 2</t>
+          <t xml:space="preserve">Adress</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -657,19 +643,19 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postadressens andra rad, valfri — slås ihop med Adress.</t>
+          <t xml:space="preserve">Postadressens första rad. Adress, Adressrad 2 och Adressrad 3 slås ihop till en adress med radbrytningar; är alla tre tomma lämnas adressen orörd.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Port C</t>
+          <t xml:space="preserve">Valsverksgatan 4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adressrad 3</t>
+          <t xml:space="preserve">Adressrad 2</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -679,19 +665,19 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postadressens tredje rad, valfri — slås ihop med Adress.</t>
+          <t xml:space="preserve">Postadressens andra rad, valfri — slås ihop med Adress.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godsmottagningen</t>
+          <t xml:space="preserve">Port C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postnummer</t>
+          <t xml:space="preserve">Adressrad 3</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -701,19 +687,19 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Postadressens tredje rad, valfri — slås ihop med Adress.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123 45</t>
+          <t xml:space="preserve">Godsmottagningen</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Postort</t>
+          <t xml:space="preserve">Postnummer</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -723,19 +709,19 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Max 20 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelby</t>
+          <t xml:space="preserve">123 45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valuta</t>
+          <t xml:space="preserve">Postort</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -745,19 +731,19 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Leverantörens katalogpriser och inköpsorder anges i valutan. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
+          <t xml:space="preserve">Max 100 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEK</t>
+          <t xml:space="preserve">Exempelby</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vårt kundnummer</t>
+          <t xml:space="preserve">Valuta</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -767,19 +753,19 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Det kundnummer leverantören har på oss, max 50 tecken — skrivs ut på förfrågan och inköpsorder. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya inköpsorder och nya katalograder (även de som Inköpspriser-importen skapar) får leverantörens valuta; befintliga behåller sin. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">K-1234</t>
+          <t xml:space="preserve">SEK</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkor</t>
+          <t xml:space="preserve">Vårt kundnummer</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -789,19 +775,19 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod och styr förfallodatum på leverantörsfakturor.</t>
+          <t xml:space="preserve">Det kundnummer leverantören har på oss, max 50 tecken — skrivs ut på förfrågan och inköpsorder. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 dagar netto</t>
+          <t xml:space="preserve">K-1234</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkor</t>
+          <t xml:space="preserve">Betalningsvillkor</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -811,19 +797,19 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
+          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod och styr förfallodatum på leverantörsfakturor.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fritt vårt lager</t>
+          <t xml:space="preserve">30 dagar netto</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveranssätt/speditör</t>
+          <t xml:space="preserve">Leveransvillkor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -833,32 +819,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
+          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelfrakt</t>
+          <t xml:space="preserve">Fritt vårt lager</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Leveranssätt/speditör</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exempelfrakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kundnummer hos speditör</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Vårt kundnummer hos leverantörens speditör, max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F-98765</t>
         </is>

--- a/apps/web/public/importmallar/importmall-leverantorer.xlsx
+++ b/apps/web/public/importmallar/importmall-leverantorer.xlsx
@@ -166,11 +166,23 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Styr leverantörsfakturans förvalda momskod när leverantören saknar egen: SE ger svensk moms, ett annat EU-land omvänd moms på varor och övriga länder varor utanför EU. Tom cell ger SE på en ny leverantör. Tom cell lämnar fältet orört på en befintlig post.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya inköpsorder och nya katalograder (även de som Inköpspriser-importen skapar) får leverantörens valuta; befintliga behåller sin. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -182,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="P1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -194,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="0">
+    <comment ref="Q1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0">
+    <comment ref="R1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -218,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="0">
+    <comment ref="S1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -302,12 +314,13 @@
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1" style="4"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="14" customWidth="1" style="4"/>
-    <col min="14" max="14" width="19" customWidth="1" style="4"/>
-    <col min="15" max="15" width="21" customWidth="1" style="4"/>
-    <col min="16" max="16" width="19" customWidth="1" style="4"/>
-    <col min="17" max="17" width="25" customWidth="1" style="4"/>
-    <col min="18" max="18" width="27" customWidth="1" style="4"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1" style="4"/>
+    <col min="15" max="15" width="19" customWidth="1" style="4"/>
+    <col min="16" max="16" width="21" customWidth="1" style="4"/>
+    <col min="17" max="17" width="19" customWidth="1" style="4"/>
+    <col min="18" max="18" width="25" customWidth="1" style="4"/>
+    <col min="19" max="19" width="27" customWidth="1" style="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -373,30 +386,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Land</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Valuta</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Vårt kundnummer</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Betalningsvillkor</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Leveransvillkor</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Leveranssätt/speditör</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kundnummer hos speditör</t>
         </is>
@@ -743,7 +761,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valuta</t>
+          <t xml:space="preserve">Land</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -753,19 +771,19 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya inköpsorder och nya katalograder (även de som Inköpspriser-importen skapar) får leverantörens valuta; befintliga behåller sin. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
+          <t xml:space="preserve">Landskod med två bokstäver (t.ex. SE); små bokstäver godtas. Styr leverantörsfakturans förvalda momskod när leverantören saknar egen: SE ger svensk moms, ett annat EU-land omvänd moms på varor och övriga länder varor utanför EU. Tom cell ger SE på en ny leverantör. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEK</t>
+          <t xml:space="preserve">SE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vårt kundnummer</t>
+          <t xml:space="preserve">Valuta</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -775,19 +793,19 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Det kundnummer leverantören har på oss, max 50 tecken — skrivs ut på förfrågan och inköpsorder. Tom cell lämnar fältet orört på en befintlig post.</t>
+          <t xml:space="preserve">Valutakod med tre bokstäver (SEK, EUR, NOK …); små bokstäver godtas, annat ger ett fel. Nya inköpsorder och nya katalograder (även de som Inköpspriser-importen skapar) får leverantörens valuta; befintliga behåller sin. Tom cell ger SEK för nya leverantörer och lämnar befintliga orörda.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">K-1234</t>
+          <t xml:space="preserve">SEK</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkor</t>
+          <t xml:space="preserve">Vårt kundnummer</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -797,19 +815,19 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod och styr förfallodatum på leverantörsfakturor.</t>
+          <t xml:space="preserve">Det kundnummer leverantören har på oss, max 50 tecken — skrivs ut på förfrågan och inköpsorder. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 dagar netto</t>
+          <t xml:space="preserve">K-1234</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkor</t>
+          <t xml:space="preserve">Betalningsvillkor</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -819,19 +837,19 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
+          <t xml:space="preserve">Betalningsvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor; börjar namnet med ett antal dagar (30 dagar netto) blir dagarna villkorets kod och styr förfallodatum på leverantörsfakturor.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fritt vårt lager</t>
+          <t xml:space="preserve">30 dagar netto</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leveranssätt/speditör</t>
+          <t xml:space="preserve">Leveransvillkor</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -841,32 +859,54 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
+          <t xml:space="preserve">Leveransvillkorets kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som nytt villkor.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exempelfrakt</t>
+          <t xml:space="preserve">Fritt vårt lager</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Leveranssätt/speditör</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speditörens kod eller namn i registret (skiftlägesokänsligt), max 100 tecken. Ett okänt värde skapas som ny speditör.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exempelfrakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kundnummer hos speditör</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nej</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Vårt kundnummer hos leverantörens speditör, max 50 tecken. Tom cell lämnar fältet orört på en befintlig post.</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F-98765</t>
         </is>
